--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126002183</v>
       </c>
       <c r="B2" t="n">
-        <v>96585</v>
+        <v>96587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126002183</v>
       </c>
       <c r="B2" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126002188</v>
       </c>
       <c r="B3" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126002183</v>
       </c>
       <c r="B2" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126002183</v>
       </c>
       <c r="B2" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126002188</v>
       </c>
       <c r="B3" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -867,6 +867,307 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126217603</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98377</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>630356</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6665385</v>
+      </c>
+      <c r="S4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126217636</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>630249</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6665436</v>
+      </c>
+      <c r="S5" t="n">
+        <v>12</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126217631</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98377</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>630359</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6665390</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126002183</v>
       </c>
       <c r="B2" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126002188</v>
       </c>
       <c r="B3" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,6 +1168,234 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126266858</v>
+      </c>
+      <c r="B7" t="n">
+        <v>95794</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>210</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>630473</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6665407</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126266857</v>
+      </c>
+      <c r="B8" t="n">
+        <v>95794</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>210</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>630461</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6665379</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126002183</v>
       </c>
       <c r="B2" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126002188</v>
       </c>
       <c r="B3" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126217603</v>
       </c>
       <c r="B4" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>126217631</v>
       </c>
       <c r="B6" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126217636</v>
+        <v>126217631</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>98379</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630249</v>
+        <v>630359</v>
       </c>
       <c r="R5" t="n">
-        <v>6665436</v>
+        <v>6665390</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126217631</v>
+        <v>126217636</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>58021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630359</v>
+        <v>630249</v>
       </c>
       <c r="R6" t="n">
-        <v>6665390</v>
+        <v>6665436</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
@@ -1144,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126002183</v>
       </c>
       <c r="B2" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126002188</v>
       </c>
       <c r="B3" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126217603</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126217631</v>
+        <v>126217636</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>58025</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630359</v>
+        <v>630249</v>
       </c>
       <c r="R5" t="n">
-        <v>6665390</v>
+        <v>6665436</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
@@ -1042,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126217636</v>
+        <v>126217631</v>
       </c>
       <c r="B6" t="n">
-        <v>58021</v>
+        <v>98383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630249</v>
+        <v>630359</v>
       </c>
       <c r="R6" t="n">
-        <v>6665436</v>
+        <v>6665390</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
@@ -1139,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,7 +1173,7 @@
         <v>126266858</v>
       </c>
       <c r="B7" t="n">
-        <v>95794</v>
+        <v>95798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>126266857</v>
       </c>
       <c r="B8" t="n">
-        <v>95794</v>
+        <v>95798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126002183</v>
       </c>
       <c r="B2" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126217603</v>
       </c>
       <c r="B4" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126217636</v>
+        <v>126217631</v>
       </c>
       <c r="B5" t="n">
-        <v>58025</v>
+        <v>98386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630249</v>
+        <v>630359</v>
       </c>
       <c r="R5" t="n">
-        <v>6665436</v>
+        <v>6665390</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126217631</v>
+        <v>126217636</v>
       </c>
       <c r="B6" t="n">
-        <v>98383</v>
+        <v>58025</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630359</v>
+        <v>630249</v>
       </c>
       <c r="R6" t="n">
-        <v>6665390</v>
+        <v>6665436</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
@@ -1144,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,7 +1173,7 @@
         <v>126266858</v>
       </c>
       <c r="B7" t="n">
-        <v>95798</v>
+        <v>95801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>126266857</v>
       </c>
       <c r="B8" t="n">
-        <v>95798</v>
+        <v>95801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126217631</v>
+        <v>126217636</v>
       </c>
       <c r="B5" t="n">
-        <v>98386</v>
+        <v>58025</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630359</v>
+        <v>630249</v>
       </c>
       <c r="R5" t="n">
-        <v>6665390</v>
+        <v>6665436</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
@@ -1042,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126217636</v>
+        <v>126217631</v>
       </c>
       <c r="B6" t="n">
-        <v>58025</v>
+        <v>98386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630249</v>
+        <v>630359</v>
       </c>
       <c r="R6" t="n">
-        <v>6665436</v>
+        <v>6665390</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
@@ -1139,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126002183</v>
       </c>
       <c r="B2" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126002188</v>
       </c>
       <c r="B3" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126217603</v>
       </c>
       <c r="B4" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126217636</v>
+        <v>126217631</v>
       </c>
       <c r="B5" t="n">
-        <v>58025</v>
+        <v>98395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630249</v>
+        <v>630359</v>
       </c>
       <c r="R5" t="n">
-        <v>6665436</v>
+        <v>6665390</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126217631</v>
+        <v>126217636</v>
       </c>
       <c r="B6" t="n">
-        <v>98386</v>
+        <v>58027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630359</v>
+        <v>630249</v>
       </c>
       <c r="R6" t="n">
-        <v>6665390</v>
+        <v>6665436</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
@@ -1144,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,7 +1173,7 @@
         <v>126266858</v>
       </c>
       <c r="B7" t="n">
-        <v>95801</v>
+        <v>95810</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>126266857</v>
       </c>
       <c r="B8" t="n">
-        <v>95801</v>
+        <v>95810</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1396,6 +1396,200 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126448724</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100543</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>630344</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6665432</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126448706</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98395</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>630405</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6665466</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126217631</v>
+        <v>126217636</v>
       </c>
       <c r="B5" t="n">
-        <v>98395</v>
+        <v>58027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630359</v>
+        <v>630249</v>
       </c>
       <c r="R5" t="n">
-        <v>6665390</v>
+        <v>6665436</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
@@ -1042,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126217636</v>
+        <v>126217631</v>
       </c>
       <c r="B6" t="n">
-        <v>58027</v>
+        <v>98395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630249</v>
+        <v>630359</v>
       </c>
       <c r="R6" t="n">
-        <v>6665436</v>
+        <v>6665390</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
@@ -1139,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126217636</v>
+        <v>126217631</v>
       </c>
       <c r="B5" t="n">
-        <v>58027</v>
+        <v>98395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630249</v>
+        <v>630359</v>
       </c>
       <c r="R5" t="n">
-        <v>6665436</v>
+        <v>6665390</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126217631</v>
+        <v>126217636</v>
       </c>
       <c r="B6" t="n">
-        <v>98395</v>
+        <v>58027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630359</v>
+        <v>630249</v>
       </c>
       <c r="R6" t="n">
-        <v>6665390</v>
+        <v>6665436</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
@@ -1144,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -1595,7 +1595,7 @@
         <v>127021128</v>
       </c>
       <c r="B11" t="n">
-        <v>100450</v>
+        <v>100525</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127021149</v>
       </c>
       <c r="B12" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>127021125</v>
       </c>
       <c r="B13" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -1595,7 +1595,7 @@
         <v>127021128</v>
       </c>
       <c r="B11" t="n">
-        <v>100525</v>
+        <v>100531</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127021149</v>
       </c>
       <c r="B12" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>127021125</v>
       </c>
       <c r="B13" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -1595,7 +1595,7 @@
         <v>127021128</v>
       </c>
       <c r="B11" t="n">
-        <v>100531</v>
+        <v>100532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127021149</v>
       </c>
       <c r="B12" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>127021125</v>
       </c>
       <c r="B13" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,7 +1595,7 @@
         <v>127021128</v>
       </c>
       <c r="B11" t="n">
-        <v>100532</v>
+        <v>100536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127021149</v>
       </c>
       <c r="B12" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>127021125</v>
       </c>
       <c r="B13" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,6 +1881,103 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127575421</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101533</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>630242</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6665380</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,7 +1595,7 @@
         <v>127021128</v>
       </c>
       <c r="B11" t="n">
-        <v>100536</v>
+        <v>100537</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127021149</v>
       </c>
       <c r="B12" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>127575421</v>
       </c>
       <c r="B14" t="n">
-        <v>101533</v>
+        <v>101534</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,6 +1978,297 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127704835</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91959</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>630425</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6665432</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127704801</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101534</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>630465</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6665403</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127704812</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>630426</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6665445</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -1595,7 +1595,7 @@
         <v>127021128</v>
       </c>
       <c r="B11" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127021149</v>
       </c>
       <c r="B12" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>127021125</v>
       </c>
       <c r="B13" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>127575421</v>
       </c>
       <c r="B14" t="n">
-        <v>101534</v>
+        <v>101536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>127704835</v>
       </c>
       <c r="B15" t="n">
-        <v>91959</v>
+        <v>91961</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,32 +2078,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127704801</v>
+        <v>127704812</v>
       </c>
       <c r="B16" t="n">
-        <v>101534</v>
+        <v>91332</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221235</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630465</v>
+        <v>630426</v>
       </c>
       <c r="R16" t="n">
-        <v>6665403</v>
+        <v>6665445</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2175,32 +2175,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127704812</v>
+        <v>127704801</v>
       </c>
       <c r="B17" t="n">
-        <v>91330</v>
+        <v>101536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>221235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630426</v>
+        <v>630465</v>
       </c>
       <c r="R17" t="n">
-        <v>6665445</v>
+        <v>6665403</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -1595,7 +1595,7 @@
         <v>127021128</v>
       </c>
       <c r="B11" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127021149</v>
       </c>
       <c r="B12" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>127021125</v>
       </c>
       <c r="B13" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>127575421</v>
       </c>
       <c r="B14" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>127704835</v>
       </c>
       <c r="B15" t="n">
-        <v>91961</v>
+        <v>91967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,32 +2078,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127704812</v>
+        <v>127704801</v>
       </c>
       <c r="B16" t="n">
-        <v>91332</v>
+        <v>101542</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630426</v>
+        <v>630465</v>
       </c>
       <c r="R16" t="n">
-        <v>6665445</v>
+        <v>6665403</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2175,32 +2175,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127704801</v>
+        <v>127704812</v>
       </c>
       <c r="B17" t="n">
-        <v>101536</v>
+        <v>91338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630465</v>
+        <v>630426</v>
       </c>
       <c r="R17" t="n">
-        <v>6665403</v>
+        <v>6665445</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -1887,7 +1887,7 @@
         <v>127575421</v>
       </c>
       <c r="B14" t="n">
-        <v>101542</v>
+        <v>101545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>127704835</v>
       </c>
       <c r="B15" t="n">
-        <v>91967</v>
+        <v>91970</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,32 +2078,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127704801</v>
+        <v>127704812</v>
       </c>
       <c r="B16" t="n">
-        <v>101542</v>
+        <v>91341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221235</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630465</v>
+        <v>630426</v>
       </c>
       <c r="R16" t="n">
-        <v>6665403</v>
+        <v>6665445</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2175,32 +2175,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127704812</v>
+        <v>127704801</v>
       </c>
       <c r="B17" t="n">
-        <v>91338</v>
+        <v>101545</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>221235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630426</v>
+        <v>630465</v>
       </c>
       <c r="R17" t="n">
-        <v>6665445</v>
+        <v>6665403</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -1887,7 +1887,7 @@
         <v>127575421</v>
       </c>
       <c r="B14" t="n">
-        <v>101545</v>
+        <v>101553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>127704835</v>
       </c>
       <c r="B15" t="n">
-        <v>91970</v>
+        <v>91978</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127704812</v>
       </c>
       <c r="B16" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127704801</v>
       </c>
       <c r="B17" t="n">
-        <v>101545</v>
+        <v>101553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -1887,7 +1887,7 @@
         <v>127575421</v>
       </c>
       <c r="B14" t="n">
-        <v>101553</v>
+        <v>101554</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>127704835</v>
       </c>
       <c r="B15" t="n">
-        <v>91978</v>
+        <v>91979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127704812</v>
       </c>
       <c r="B16" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127704801</v>
       </c>
       <c r="B17" t="n">
-        <v>101553</v>
+        <v>101554</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -1887,7 +1887,7 @@
         <v>127575421</v>
       </c>
       <c r="B14" t="n">
-        <v>101554</v>
+        <v>101555</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>127704835</v>
       </c>
       <c r="B15" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127704812</v>
       </c>
       <c r="B16" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127704801</v>
       </c>
       <c r="B17" t="n">
-        <v>101554</v>
+        <v>101555</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -1887,7 +1887,7 @@
         <v>127575421</v>
       </c>
       <c r="B14" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>127704835</v>
       </c>
       <c r="B15" t="n">
-        <v>91980</v>
+        <v>91981</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127704812</v>
       </c>
       <c r="B16" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127704801</v>
       </c>
       <c r="B17" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -2078,32 +2078,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127704812</v>
+        <v>127704801</v>
       </c>
       <c r="B16" t="n">
-        <v>91352</v>
+        <v>101556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630426</v>
+        <v>630465</v>
       </c>
       <c r="R16" t="n">
-        <v>6665445</v>
+        <v>6665403</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2175,32 +2175,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127704801</v>
+        <v>127704812</v>
       </c>
       <c r="B17" t="n">
-        <v>101556</v>
+        <v>91352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630465</v>
+        <v>630426</v>
       </c>
       <c r="R17" t="n">
-        <v>6665403</v>
+        <v>6665445</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -1984,7 +1984,7 @@
         <v>127704835</v>
       </c>
       <c r="B15" t="n">
-        <v>91981</v>
+        <v>91989</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127704801</v>
       </c>
       <c r="B16" t="n">
-        <v>101556</v>
+        <v>101564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127704812</v>
       </c>
       <c r="B17" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1984,7 +1984,7 @@
         <v>127704835</v>
       </c>
       <c r="B15" t="n">
-        <v>91989</v>
+        <v>92000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127704801</v>
       </c>
       <c r="B16" t="n">
-        <v>101564</v>
+        <v>101576</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127704812</v>
       </c>
       <c r="B17" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,6 +2269,318 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128493969</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>630409</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6665495</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128493975</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57698</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>630413</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6665435</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hördes ropa från asptopp, flög sedan norrut och hördes därefter vid ett flertal tillfällen</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128603976</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101657</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>630252</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6665421</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27281-2025 artfynd.xlsx
+++ b/artfynd/A 27281-2025 artfynd.xlsx
@@ -2275,7 +2275,7 @@
         <v>128493969</v>
       </c>
       <c r="B18" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>128493975</v>
       </c>
       <c r="B19" t="n">
-        <v>57698</v>
+        <v>57702</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>128603976</v>
       </c>
       <c r="B20" t="n">
-        <v>101657</v>
+        <v>101665</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
